--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>物品类型</t>
+  </si>
+  <si>
+    <t>堆叠数</t>
+  </si>
+  <si>
+    <t>格子</t>
   </si>
   <si>
     <t>金币</t>
@@ -1320,16 +1326,28 @@
       <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="B4" s="2">
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -77,7 +77,16 @@
     <t>格子</t>
   </si>
   <si>
-    <t>金币</t>
+    <t>黄金</t>
+  </si>
+  <si>
+    <t>白银</t>
+  </si>
+  <si>
+    <t>铜钱</t>
+  </si>
+  <si>
+    <t>改名卡</t>
   </si>
 </sst>
 </file>
@@ -1265,8 +1274,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1304,7 +1313,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
@@ -1347,6 +1356,57 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="2">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="2">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1355,19 +1415,28 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  <conditionalFormatting sqref="B1:B3 B7 B9:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,15 @@
   </si>
   <si>
     <t>改名卡</t>
+  </si>
+  <si>
+    <t>默认头像</t>
+  </si>
+  <si>
+    <t>默认头像框</t>
+  </si>
+  <si>
+    <t>默认称号</t>
   </si>
 </sst>
 </file>
@@ -1274,8 +1283,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1344,12 +1353,13 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:6">
       <c r="B4" s="2">
-        <v>10001</v>
+        <v>100001</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="2">
+        <f>IF(B4="","",INT(B4/100000))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
@@ -1361,12 +1371,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="B5" s="2">
-        <v>10002</v>
+        <v>100002</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="2">
+        <f t="shared" ref="D5:D14" si="0">IF(B5="","",INT(B5/100000))</f>
         <v>1</v>
       </c>
       <c r="E5" s="2">
@@ -1378,12 +1389,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="B6" s="2">
-        <v>10003</v>
+        <v>100003</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E6" s="2">
@@ -1391,16 +1403,23 @@
       </c>
       <c r="F6" s="2" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" s="2">
-        <v>20001</v>
+        <v>110001</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E8" s="2">
@@ -1410,33 +1429,111 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:6">
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="2">
+        <v>400001</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="2">
+        <v>500001</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="2">
+        <v>600001</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F4" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F14" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
+  <conditionalFormatting sqref="F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B12">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B14">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+  <conditionalFormatting sqref="B1:B3 B7 B9:B11 B13 B15:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -47,6 +47,9 @@
     <t>stacked</t>
   </si>
   <si>
+    <t>quality</t>
+  </si>
+  <si>
     <t>squares</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>quality_type</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -72,6 +78,9 @@
   </si>
   <si>
     <t>堆叠数</t>
+  </si>
+  <si>
+    <t>品质</t>
   </si>
   <si>
     <t>格子</t>
@@ -1283,18 +1292,18 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
-    <col min="4" max="5" width="26" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="4" max="6" width="26" style="2" customWidth="1"/>
+    <col min="7" max="7" width="40.375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:6">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1313,50 +1322,59 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:6">
+    <row r="4" s="2" customFormat="1" spans="1:7">
       <c r="B4" s="2">
         <v>100001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2">
         <f>IF(B4="","",INT(B4/100000))</f>
@@ -1365,16 +1383,19 @@
       <c r="E4" s="2">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="b">
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="B5" s="2">
         <v>100002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" ref="D5:D14" si="0">IF(B5="","",INT(B5/100000))</f>
@@ -1383,16 +1404,19 @@
       <c r="E5" s="2">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="b">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="B6" s="2">
         <v>100003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
@@ -1401,22 +1425,25 @@
       <c r="E6" s="2">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="b">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="B8" s="2">
         <v>110001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
@@ -1425,22 +1452,25 @@
       <c r="E8" s="2">
         <v>0</v>
       </c>
-      <c r="F8" s="2" t="b">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="D9" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="B10" s="2">
         <v>400001</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
@@ -1449,22 +1479,25 @@
       <c r="E10" s="2">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="b">
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="D11" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="B12" s="2">
         <v>500001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D12" s="2">
         <f t="shared" si="0"/>
@@ -1473,22 +1506,25 @@
       <c r="E12" s="2">
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="b">
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="D13" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="B14" s="2">
         <v>600001</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2">
         <f t="shared" si="0"/>
@@ -1497,21 +1533,24 @@
       <c r="E14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="b">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:F14" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G14" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
+  <conditionalFormatting sqref="E3:F3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+  <conditionalFormatting sqref="G3">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4">

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -53,6 +53,9 @@
     <t>squares</t>
   </si>
   <si>
+    <t>unlock_task_id</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t>格子</t>
   </si>
   <si>
+    <t>解锁条件id</t>
+  </si>
+  <si>
     <t>黄金</t>
   </si>
   <si>
@@ -99,6 +105,39 @@
   </si>
   <si>
     <t>默认头像</t>
+  </si>
+  <si>
+    <t>头像-1</t>
+  </si>
+  <si>
+    <t>头像-2</t>
+  </si>
+  <si>
+    <t>头像-3</t>
+  </si>
+  <si>
+    <t>头像-4</t>
+  </si>
+  <si>
+    <t>头像-5</t>
+  </si>
+  <si>
+    <t>头像-6</t>
+  </si>
+  <si>
+    <t>头像-7</t>
+  </si>
+  <si>
+    <t>头像-8</t>
+  </si>
+  <si>
+    <t>头像-9</t>
+  </si>
+  <si>
+    <t>头像-10</t>
+  </si>
+  <si>
+    <t>头像-11</t>
   </si>
   <si>
     <t>默认头像框</t>
@@ -1292,18 +1331,19 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
     <col min="4" max="6" width="26" style="2" customWidth="1"/>
     <col min="7" max="7" width="40.375" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="15" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1325,56 +1365,65 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:7">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:7">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:8">
       <c r="B4" s="2">
         <v>100001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="2">
         <f>IF(B4="","",INT(B4/100000))</f>
@@ -1390,12 +1439,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="B5" s="2">
         <v>100002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" ref="D5:D14" si="0">IF(B5="","",INT(B5/100000))</f>
@@ -1411,12 +1460,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="B6" s="2">
         <v>100003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
@@ -1432,18 +1481,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="B8" s="2">
         <v>110001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
@@ -1459,18 +1508,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="D9" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="B10" s="2">
         <v>400001</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
@@ -1486,93 +1535,360 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="D11" s="2" t="str">
+    <row r="11" s="2" customFormat="1" spans="1:8">
+      <c r="B11" s="2">
+        <v>400002</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2">
         <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3003001</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:8">
+      <c r="B12" s="2">
+        <v>400003</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2">
+        <f>IF(B12="","",INT(B12/100000))</f>
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3003002</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:8">
+      <c r="B13" s="2">
+        <v>400004</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" ref="D13:D21" si="1">IF(B13="","",INT(B13/100000))</f>
+        <v>4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>3003003</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:8">
+      <c r="B14" s="2">
+        <v>400005</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3003004</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:8">
+      <c r="B15" s="2">
+        <v>400006</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>3003005</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:8">
+      <c r="B16" s="2">
+        <v>400007</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3003006</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:8">
+      <c r="B17" s="2">
+        <v>400008</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>3003007</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="2:8">
+      <c r="B18" s="2">
+        <v>400009</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>3003008</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:8">
+      <c r="B19" s="2">
+        <v>400010</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>3003009</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:8">
+      <c r="B20" s="2">
+        <v>400011</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>3003010</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="2:8">
+      <c r="B21" s="2">
+        <v>400012</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>3003011</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="D22" s="2" t="str">
+        <f>IF(B22="","",INT(B22/100000))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="2">
+    <row r="23" spans="2:8">
+      <c r="B23" s="2">
         <v>500001</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2">
-        <f t="shared" si="0"/>
+      <c r="C23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="2">
+        <f>IF(B23="","",INT(B23/100000))</f>
         <v>5</v>
       </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="D13" s="2" t="str">
-        <f t="shared" si="0"/>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="D24" s="2" t="str">
+        <f>IF(B24="","",INT(B24/100000))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="2">
+    <row r="25" spans="2:8">
+      <c r="B25" s="2">
         <v>600001</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="0"/>
+      <c r="C25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="2">
+        <f>IF(B25="","",INT(B25/100000))</f>
         <v>6</v>
       </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="b">
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G14" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G25" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B23">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
+  <conditionalFormatting sqref="B25">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
+  <conditionalFormatting sqref="B11:B21">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B11 B13 B15:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  <conditionalFormatting sqref="B1:B3 B7 B9:B10 B22 B24 B26:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -107,43 +107,58 @@
     <t>默认头像</t>
   </si>
   <si>
-    <t>头像-1</t>
-  </si>
-  <si>
-    <t>头像-2</t>
-  </si>
-  <si>
-    <t>头像-3</t>
-  </si>
-  <si>
-    <t>头像-4</t>
-  </si>
-  <si>
-    <t>头像-5</t>
-  </si>
-  <si>
-    <t>头像-6</t>
-  </si>
-  <si>
-    <t>头像-7</t>
-  </si>
-  <si>
-    <t>头像-8</t>
-  </si>
-  <si>
-    <t>头像-9</t>
-  </si>
-  <si>
-    <t>头像-10</t>
-  </si>
-  <si>
-    <t>头像-11</t>
+    <t>头像-嬴政</t>
+  </si>
+  <si>
+    <t>头像-刘彻</t>
+  </si>
+  <si>
+    <t>头像-李世民</t>
+  </si>
+  <si>
+    <t>头像-赵飞燕</t>
+  </si>
+  <si>
+    <t>头像-蔡文姬</t>
+  </si>
+  <si>
+    <t>头像-杨玉环</t>
+  </si>
+  <si>
+    <t>头像-白起</t>
+  </si>
+  <si>
+    <t>头像-张骞</t>
   </si>
   <si>
     <t>默认头像框</t>
   </si>
   <si>
     <t>默认称号</t>
+  </si>
+  <si>
+    <t>嬴政</t>
+  </si>
+  <si>
+    <t>刘彻</t>
+  </si>
+  <si>
+    <t>李世民</t>
+  </si>
+  <si>
+    <t>赵飞燕</t>
+  </si>
+  <si>
+    <t>蔡文姬</t>
+  </si>
+  <si>
+    <t>杨玉环</t>
+  </si>
+  <si>
+    <t>白起</t>
+  </si>
+  <si>
+    <t>张骞</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1346,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1420,19 +1435,20 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:8">
       <c r="B4" s="2">
-        <v>100001</v>
+        <v>1001001</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="2">
-        <f>IF(B4="","",INT(B4/100000))</f>
+        <f t="shared" ref="D4:D12" si="0">IF(B4="","",INT(B4/1000000))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
+        <f t="shared" ref="F4:F11" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G4" s="2" t="b">
@@ -1441,19 +1457,20 @@
     </row>
     <row r="5" spans="1:8">
       <c r="B5" s="2">
-        <v>100002</v>
+        <v>1001002</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" ref="D5:D14" si="0">IF(B5="","",INT(B5/100000))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G5" s="2" t="b">
@@ -1462,7 +1479,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="2">
-        <v>100003</v>
+        <v>1001003</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>22</v>
@@ -1475,6 +1492,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G6" s="2" t="b">
@@ -1486,10 +1504,14 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="2">
-        <v>110001</v>
+        <v>1011001</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>23</v>
@@ -1502,6 +1524,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G8" s="2" t="b">
@@ -1513,10 +1536,14 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="2">
-        <v>400001</v>
+        <v>4011001</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
@@ -1529,366 +1556,617 @@
         <v>0</v>
       </c>
       <c r="F10" s="2">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G10" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" spans="1:8">
-      <c r="B11" s="2">
-        <v>400002</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3003001</v>
-      </c>
+    <row r="11" customFormat="1" spans="1:8">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:8">
       <c r="B12" s="2">
-        <v>400003</v>
+        <v>4024001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2">
-        <f>IF(B12="","",INT(B12/100000))</f>
+        <f>IF(B12="","",INT(B12/1000000))</f>
         <v>4</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <f>IF(B12="","",MOD(INT(B12/1000),10))</f>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>3003002</v>
+        <v>300324001</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:8">
       <c r="B13" s="2">
-        <v>400004</v>
+        <v>4024002</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" ref="D13:D21" si="1">IF(B13="","",INT(B13/100000))</f>
+        <f t="shared" ref="D12:D18" si="2">IF(B13="","",INT(B13/1000000))</f>
         <v>4</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <f t="shared" ref="F13:F34" si="3">IF(B13="","",MOD(INT(B13/1000),10))</f>
+        <v>4</v>
       </c>
       <c r="G13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>3003003</v>
+        <v>300324002</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:8">
       <c r="B14" s="2">
-        <v>400005</v>
+        <v>4024003</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H14" s="2">
-        <v>3003004</v>
+        <v>300324003</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:8">
-      <c r="B15" s="2">
-        <v>400006</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3003005</v>
+      <c r="F15" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:8">
       <c r="B16" s="2">
-        <v>400007</v>
+        <v>4034001</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>3003006</v>
+        <v>300334001</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="2:8">
       <c r="B17" s="2">
-        <v>400008</v>
+        <v>4034002</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>300334002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="2">
+        <v>4034003</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>300334003</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="D19" s="2" t="str">
+        <f>IF(B19="","",INT(B19/1000000))</f>
+        <v/>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="2">
+        <v>4044001</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="D20" s="2">
+        <f>IF(B20="","",INT(B20/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>300344001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="2">
+        <v>4044002</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2">
+        <f>IF(B21="","",INT(B21/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>300344002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="2">
+        <v>4044003</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="2">
+        <f>IF(B22="","",INT(B22/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>300344003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="F23" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="2">
+        <v>5001001</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="2">
+        <f>IF(B24="","",INT(B24/1000000))</f>
+        <v>5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>3003007</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:8">
-      <c r="B18" s="2">
-        <v>400009</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="D25" s="2" t="str">
+        <f>IF(B25="","",INT(B25/1000000))</f>
+        <v/>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="2">
+        <v>6001001</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2">
+        <f>IF(B26="","",INT(B26/1000000))</f>
+        <v>6</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>3003008</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:8">
-      <c r="B19" s="2">
-        <v>400010</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>3003009</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
-      <c r="B20" s="2">
-        <v>400011</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
-        <v>3003010</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="2:8">
-      <c r="B21" s="2">
-        <v>400012</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="D27" s="2" t="str">
+        <f>IF(B27="","",INT(B27/1000000))</f>
+        <v/>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>3003011</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="D22" s="2" t="str">
-        <f>IF(B22="","",INT(B22/100000))</f>
+      <c r="D28" s="2">
+        <f>IF(B28="","",INT(B28/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="2">
+        <v>7024002</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="2">
+        <f>IF(B29="","",INT(B29/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="2">
+        <v>7024003</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="2">
+        <f>IF(B30="","",INT(B30/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="D31" s="2" t="str">
+        <f>IF(B31="","",INT(B31/1000000))</f>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="2">
-        <v>500001</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="2">
-        <f>IF(B23="","",INT(B23/100000))</f>
-        <v>5</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="D24" s="2" t="str">
-        <f>IF(B24="","",INT(B24/100000))</f>
+      <c r="F31" s="2" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="2">
-        <v>600001</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="2">
-        <f>IF(B25="","",INT(B25/100000))</f>
-        <v>6</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="b">
+    <row r="32" spans="2:8">
+      <c r="B32" s="2">
+        <v>7034001</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="2">
+        <f>IF(B32="","",INT(B32/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="2">
+        <v>7034002</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="2">
+        <f>IF(B33="","",INT(B33/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="2">
+        <v>7034003</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="2">
+        <f>IF(B34="","",INT(B34/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="D35" s="2" t="str">
+        <f>IF(B35="","",INT(B35/1000000))</f>
+        <v/>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f>IF(B35="","",MOD(INT(B35/1000),10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="2">
+        <v>7044001</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="2">
+        <f>IF(B36="","",INT(B36/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(B36="","",MOD(INT(B36/1000),10))</f>
+        <v>4</v>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="2">
+        <v>7044002</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="2">
+        <f>IF(B37="","",INT(B37/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <f>IF(B37="","",MOD(INT(B37/1000),10))</f>
+        <v>4</v>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="2">
+        <v>7044003</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="2">
+        <f>IF(B38="","",INT(B38/1000000))</f>
+        <v>7</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <f>IF(B38="","",MOD(INT(B38/1000),10))</f>
+        <v>4</v>
+      </c>
+      <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G25" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G26" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12:B15">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B22">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:F3">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="B36:B38">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
+  <conditionalFormatting sqref="H12:H14">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
+  <conditionalFormatting sqref="H16:H18">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B21">
+  <conditionalFormatting sqref="H20:H22">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B10 B22 B24 B26:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  <conditionalFormatting sqref="B1:B3 B7 B9 B25 B27 B31:B35 B39:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15 H19">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -131,6 +131,9 @@
     <t>头像-张骞</t>
   </si>
   <si>
+    <t>头像-房玄龄</t>
+  </si>
+  <si>
     <t>默认头像框</t>
   </si>
   <si>
@@ -159,6 +162,9 @@
   </si>
   <si>
     <t>张骞</t>
+  </si>
+  <si>
+    <t>房玄龄</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F11" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <f t="shared" ref="F4:F12" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G4" s="2" t="b">
@@ -1590,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="2">
-        <f>IF(B12="","",MOD(INT(B12/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G12" s="2" t="b">
@@ -1608,14 +1614,14 @@
         <v>26</v>
       </c>
       <c r="D13" s="2">
-        <f t="shared" ref="D12:D18" si="2">IF(B13="","",INT(B13/1000000))</f>
+        <f t="shared" ref="D12:D22" si="2">IF(B13="","",INT(B13/1000000))</f>
         <v>4</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" ref="F13:F34" si="3">IF(B13="","",MOD(INT(B13/1000),10))</f>
+        <f t="shared" ref="F13:F38" si="3">IF(B13="","",MOD(INT(B13/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G13" s="2" t="b">
@@ -1733,7 +1739,7 @@
     </row>
     <row r="19" spans="2:8">
       <c r="D19" s="2" t="str">
-        <f>IF(B19="","",INT(B19/1000000))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="F19" s="2" t="str">
@@ -1749,7 +1755,7 @@
         <v>31</v>
       </c>
       <c r="D20" s="2">
-        <f>IF(B20="","",INT(B20/1000000))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="E20" s="2">
@@ -1774,7 +1780,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2">
-        <f>IF(B21="","",INT(B21/1000000))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="E21" s="2">
@@ -1796,10 +1802,10 @@
         <v>4044003</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2">
-        <f>IF(B22="","",INT(B22/1000000))</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="E22" s="2">
@@ -1827,10 +1833,10 @@
         <v>5001001</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="2">
-        <f>IF(B24="","",INT(B24/1000000))</f>
+        <f t="shared" ref="D24:D38" si="4">IF(B24="","",INT(B24/1000000))</f>
         <v>5</v>
       </c>
       <c r="E24" s="2">
@@ -1846,7 +1852,7 @@
     </row>
     <row r="25" spans="2:8">
       <c r="D25" s="2" t="str">
-        <f>IF(B25="","",INT(B25/1000000))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F25" s="2" t="str">
@@ -1859,10 +1865,10 @@
         <v>6001001</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" s="2">
-        <f>IF(B26="","",INT(B26/1000000))</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="E26" s="2">
@@ -1878,7 +1884,7 @@
     </row>
     <row r="27" spans="2:8">
       <c r="D27" s="2" t="str">
-        <f>IF(B27="","",INT(B27/1000000))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F27" s="2" t="str">
@@ -1891,10 +1897,10 @@
         <v>7024001</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" s="2">
-        <f>IF(B28="","",INT(B28/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E28" s="2">
@@ -1913,10 +1919,10 @@
         <v>7024002</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2">
-        <f>IF(B29="","",INT(B29/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E29" s="2">
@@ -1935,10 +1941,10 @@
         <v>7024003</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D30" s="2">
-        <f>IF(B30="","",INT(B30/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E30" s="2">
@@ -1954,7 +1960,7 @@
     </row>
     <row r="31" spans="2:8">
       <c r="D31" s="2" t="str">
-        <f>IF(B31="","",INT(B31/1000000))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F31" s="2" t="str">
@@ -1967,10 +1973,10 @@
         <v>7034001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2">
-        <f>IF(B32="","",INT(B32/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E32" s="2">
@@ -1989,10 +1995,10 @@
         <v>7034002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2">
-        <f>IF(B33="","",INT(B33/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E33" s="2">
@@ -2011,10 +2017,10 @@
         <v>7034003</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D34" s="2">
-        <f>IF(B34="","",INT(B34/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E34" s="2">
@@ -2030,11 +2036,11 @@
     </row>
     <row r="35" spans="2:7">
       <c r="D35" s="2" t="str">
-        <f>IF(B35="","",INT(B35/1000000))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="F35" s="2" t="str">
-        <f>IF(B35="","",MOD(INT(B35/1000),10))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2043,17 +2049,17 @@
         <v>7044001</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D36" s="2">
-        <f>IF(B36="","",INT(B36/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <f>IF(B36="","",MOD(INT(B36/1000),10))</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="G36" s="2" t="b">
@@ -2065,17 +2071,17 @@
         <v>7044002</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D37" s="2">
-        <f>IF(B37="","",INT(B37/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <f>IF(B37="","",MOD(INT(B37/1000),10))</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="G37" s="2" t="b">
@@ -2087,17 +2093,17 @@
         <v>7044003</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2">
-        <f>IF(B38="","",INT(B38/1000000))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
       </c>
       <c r="F38" s="2">
-        <f>IF(B38="","",MOD(INT(B38/1000),10))</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="G38" s="2" t="b">
@@ -2105,7 +2111,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G26" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G38" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -1830,7 +1830,7 @@
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="2">
-        <v>5001001</v>
+        <v>5011001</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>34</v>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,24 @@
   </si>
   <si>
     <t>默认头像框</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>橙</t>
+  </si>
+  <si>
+    <t>红</t>
   </si>
   <si>
     <t>默认称号</t>
@@ -1352,7 +1370,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1621,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" ref="F13:F38" si="3">IF(B13="","",MOD(INT(B13/1000),10))</f>
+        <f>IF(B13="","",MOD(INT(B13/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G13" s="2" t="b">
@@ -1646,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B14="","",MOD(INT(B14/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G14" s="2" t="b">
@@ -1658,7 +1676,7 @@
     </row>
     <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="F15" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(B15="","",MOD(INT(B15/1000),10))</f>
         <v/>
       </c>
     </row>
@@ -1677,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B16="","",MOD(INT(B16/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G16" s="2" t="b">
@@ -1702,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B17="","",MOD(INT(B17/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G17" s="2" t="b">
@@ -1727,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B18="","",MOD(INT(B18/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G18" s="2" t="b">
@@ -1743,7 +1761,7 @@
         <v/>
       </c>
       <c r="F19" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(B19="","",MOD(INT(B19/1000),10))</f>
         <v/>
       </c>
     </row>
@@ -1762,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B20="","",MOD(INT(B20/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G20" s="2" t="b">
@@ -1787,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B21="","",MOD(INT(B21/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G21" s="2" t="b">
@@ -1812,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2">
-        <f t="shared" si="3"/>
+        <f>IF(B22="","",MOD(INT(B22/1000),10))</f>
         <v>4</v>
       </c>
       <c r="G22" s="2" t="b">
@@ -1824,7 +1842,7 @@
     </row>
     <row r="23" spans="2:8">
       <c r="F23" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(B23="","",MOD(INT(B23/1000),10))</f>
         <v/>
       </c>
     </row>
@@ -1836,123 +1854,147 @@
         <v>34</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" ref="D24:D38" si="4">IF(B24="","",INT(B24/1000000))</f>
+        <f>IF(B24="","",INT(B24/1000000))</f>
         <v>5</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="2">
+        <f>IF(B24="","",MOD(INT(B24/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="2:8">
+      <c r="B25" s="2">
+        <v>5011002</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" ref="D25:D30" si="3">IF(B25="","",INT(B25/1000000))</f>
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" ref="F25:F30" si="4">IF(B25="","",MOD(INT(B25/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="2:8">
+      <c r="B26" s="2">
+        <v>5011003</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="2">
         <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G24" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="D25" s="2" t="str">
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="2:8">
+      <c r="B27" s="2">
+        <v>5011004</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="F25" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="2:8">
+      <c r="B28" s="2">
+        <v>5011005</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="2">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="2">
-        <v>6001001</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="2">
+        <v>5</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="2:8">
+      <c r="B29" s="2">
+        <v>5011006</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="2">
         <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G26" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="D27" s="2" t="str">
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="2:8">
+      <c r="B30" s="2">
+        <v>5011007</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="F27" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="2">
-        <v>7024001</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="G28" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="2">
-        <v>7024002</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="G29" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="2">
-        <v>7024003</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2" t="b">
         <v>0</v>
@@ -1960,74 +2002,62 @@
     </row>
     <row r="31" spans="2:8">
       <c r="D31" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D31:D44" si="5">IF(B31="","",INT(B31/1000000))</f>
         <v/>
       </c>
       <c r="F31" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F31:F44" si="6">IF(B31="","",MOD(INT(B31/1000),10))</f>
         <v/>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="2">
-        <v>7034001</v>
+        <v>6001001</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D32" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
       </c>
       <c r="F32" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="2">
-        <v>7034002</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="E33" s="2">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="G33" s="2" t="b">
-        <v>0</v>
+      <c r="D33" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="2">
-        <v>7034003</v>
+        <v>7024001</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="G34" s="2" t="b">
@@ -2035,31 +2065,43 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="D35" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="F35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="B35" s="2">
+        <v>7024002</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="2">
-        <v>7044001</v>
+        <v>7024003</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
       </c>
       <c r="F36" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="G36" s="2" t="b">
@@ -2067,112 +2109,223 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="2">
-        <v>7044002</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="2">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="E37" s="2">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="G37" s="2" t="b">
-        <v>0</v>
+      <c r="D37" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="2">
+        <v>7034001</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="2">
+        <v>7034002</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="2">
+        <v>7034003</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="D41" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="2">
+        <v>7044001</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="2">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="2">
+        <v>7044002</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="2">
         <v>7044003</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="2">
-        <f t="shared" si="4"/>
+      <c r="C44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="2">
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="G38" s="2" t="b">
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G38" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G44" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  <conditionalFormatting sqref="B12:B15">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:B15">
+  <conditionalFormatting sqref="B16:B22">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B22">
+  <conditionalFormatting sqref="B25:B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B44">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B36:B38">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="H12:H14">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H14">
+  <conditionalFormatting sqref="H16:H18">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16:H18">
+  <conditionalFormatting sqref="H20:H22">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20:H22">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9 B25 B27 B31:B35 B39:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+  <conditionalFormatting sqref="B1:B3 B7 B9 B31 B33 B37:B41 B45:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15 H19">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -137,22 +137,22 @@
     <t>默认头像框</t>
   </si>
   <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>绿</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>橙</t>
-  </si>
-  <si>
-    <t>红</t>
+    <t>头像框-白</t>
+  </si>
+  <si>
+    <t>头像框-绿</t>
+  </si>
+  <si>
+    <t>头像框-蓝</t>
+  </si>
+  <si>
+    <t>头像框-紫</t>
+  </si>
+  <si>
+    <t>头像框-橙</t>
+  </si>
+  <si>
+    <t>头像框-红</t>
   </si>
   <si>
     <t>默认称号</t>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F12" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <f t="shared" ref="F4:F24" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G4" s="2" t="b">
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2">
-        <f>IF(B13="","",MOD(INT(B13/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G13" s="2" t="b">
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2">
-        <f>IF(B14="","",MOD(INT(B14/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G14" s="2" t="b">
@@ -1676,7 +1676,7 @@
     </row>
     <row r="15" s="2" customFormat="1" spans="1:8">
       <c r="F15" s="2" t="str">
-        <f>IF(B15="","",MOD(INT(B15/1000),10))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
-        <f>IF(B16="","",MOD(INT(B16/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G16" s="2" t="b">
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2">
-        <f>IF(B17="","",MOD(INT(B17/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G17" s="2" t="b">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="2">
-        <f>IF(B18="","",MOD(INT(B18/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G18" s="2" t="b">
@@ -1761,7 +1761,7 @@
         <v/>
       </c>
       <c r="F19" s="2" t="str">
-        <f>IF(B19="","",MOD(INT(B19/1000),10))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2">
-        <f>IF(B20="","",MOD(INT(B20/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G20" s="2" t="b">
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <f>IF(B21="","",MOD(INT(B21/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G21" s="2" t="b">
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2">
-        <f>IF(B22="","",MOD(INT(B22/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="G22" s="2" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="23" spans="2:8">
       <c r="F23" s="2" t="str">
-        <f>IF(B23="","",MOD(INT(B23/1000),10))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2">
-        <f>IF(B24="","",MOD(INT(B24/1000),10))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G24" s="2" t="b">
@@ -1889,6 +1889,9 @@
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="H25" s="2">
+        <v>400311002</v>
+      </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="2:8">
       <c r="B26" s="2">
@@ -1911,6 +1914,9 @@
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="H26" s="2">
+        <v>400311003</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1" spans="2:8">
       <c r="B27" s="2">
@@ -1933,6 +1939,9 @@
       <c r="G27" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="H27" s="2">
+        <v>400311004</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1" spans="2:8">
       <c r="B28" s="2">
@@ -1955,6 +1964,9 @@
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="H28" s="2">
+        <v>400311005</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1" spans="2:8">
       <c r="B29" s="2">
@@ -1977,6 +1989,9 @@
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="H29" s="2">
+        <v>400311006</v>
+      </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="2:8">
       <c r="B30" s="2">
@@ -1998,6 +2013,9 @@
       </c>
       <c r="G30" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>400311007</v>
       </c>
     </row>
     <row r="31" spans="2:8">
@@ -2265,67 +2283,70 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B23">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="B12:B15">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12:B15">
+  <conditionalFormatting sqref="B16:B22">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B22">
+  <conditionalFormatting sqref="B25:B30">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B42:B44">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B30">
+  <conditionalFormatting sqref="H12:H14">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16:H18">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20:H22">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H30">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H14">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16:H18">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20:H22">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B3 B7 B9 B31 B33 B37:B41 B45:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15 H19">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -56,6 +56,12 @@
     <t>unlock_task_id</t>
   </si>
   <si>
+    <t>parameter0</t>
+  </si>
+  <si>
+    <t>parameter1</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -92,6 +98,12 @@
     <t>解锁条件id</t>
   </si>
   <si>
+    <t>关联参数0</t>
+  </si>
+  <si>
+    <t>关联参数1</t>
+  </si>
+  <si>
     <t>黄金</t>
   </si>
   <si>
@@ -104,6 +116,18 @@
     <t>改名卡</t>
   </si>
   <si>
+    <t>粮食</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>石头</t>
+  </si>
+  <si>
+    <t>铁矿</t>
+  </si>
+  <si>
     <t>默认头像</t>
   </si>
   <si>
@@ -183,6 +207,12 @@
   </si>
   <si>
     <t>房玄龄</t>
+  </si>
+  <si>
+    <t>人物经验</t>
+  </si>
+  <si>
+    <t>vip经验</t>
   </si>
 </sst>
 </file>
@@ -1370,8 +1400,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1379,10 +1409,11 @@
     <col min="4" max="6" width="26" style="2" customWidth="1"/>
     <col min="7" max="7" width="40.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="15" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="12.25" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1407,84 +1438,102 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:8">
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:8">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:10">
       <c r="B4" s="2">
         <v>1001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" ref="D4:D12" si="0">IF(B4="","",INT(B4/1000000))</f>
+        <f t="shared" ref="D4:D13" si="0">IF(B4="","",INT(B4/1000000))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F24" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <f t="shared" ref="F4:F9" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="B5" s="2">
         <v>1001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="0"/>
@@ -1501,12 +1550,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="B6" s="2">
         <v>1001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="0"/>
@@ -1523,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:10">
       <c r="D7" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1533,12 +1582,12 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="B8" s="2">
         <v>1011001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="0"/>
@@ -1555,7 +1604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="D9" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1565,788 +1614,938 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="B10" s="2">
-        <v>4011001</v>
+        <v>1021001</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G10" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:8">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="str">
-        <f t="shared" si="1"/>
+    <row r="11" spans="1:10">
+      <c r="B11" s="2">
+        <v>1021002</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="2">
+        <v>1021003</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="2">
+        <v>1021004</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="2">
+        <v>4011001</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2">
+        <f>IF(B15="","",INT(B15/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" ref="F15:F29" si="2">IF(B15="","",MOD(INT(B15/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:10">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="1:8">
-      <c r="B12" s="2">
-        <v>4024001</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="2">
-        <f>IF(B12="","",INT(B12/1000000))</f>
-        <v>4</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>300324001</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="1:8">
-      <c r="B13" s="2">
-        <v>4024002</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="2">
-        <f t="shared" ref="D12:D22" si="2">IF(B13="","",INT(B13/1000000))</f>
-        <v>4</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>300324002</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="1:8">
-      <c r="B14" s="2">
-        <v>4024003</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>300324003</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:8">
-      <c r="F15" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:8">
-      <c r="B16" s="2">
-        <v>4034001</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>300334001</v>
-      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="2:8">
       <c r="B17" s="2">
-        <v>4034002</v>
+        <v>4024001</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2">
+        <f>IF(B17="","",INT(B17/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
       <c r="G17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>300334002</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
+        <v>300324001</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="2:8">
       <c r="B18" s="2">
-        <v>4034003</v>
+        <v>4024002</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D18" s="2">
+        <f t="shared" ref="D17:D27" si="3">IF(B18="","",INT(B18/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
       <c r="G18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="2">
-        <v>300334003</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="D19" s="2" t="str">
+        <v>300324002</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="2:8">
+      <c r="B19" s="2">
+        <v>4024003</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>300324003</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:8">
+      <c r="F20" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F19" s="2" t="str">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="2:8">
+      <c r="B21" s="2">
+        <v>4034001</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>300334001</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="2:8">
+      <c r="B22" s="2">
+        <v>4034002</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>300334002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="2">
+        <v>4034003</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>300334003</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="2">
+      <c r="F24" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="2">
         <v>4044001</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="2">
+      <c r="C25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
         <v>300344001</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="2">
+    <row r="26" spans="2:8">
+      <c r="B26" s="2">
         <v>4044002</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>300344002</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="2">
-        <v>4044003</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>300344003</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="F23" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="2">
-        <v>5011001</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="2">
-        <f>IF(B24="","",INT(B24/1000000))</f>
-        <v>5</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="2:8">
-      <c r="B25" s="2">
-        <v>5011002</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="2">
-        <f t="shared" ref="D25:D30" si="3">IF(B25="","",INT(B25/1000000))</f>
-        <v>5</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <f t="shared" ref="F25:F30" si="4">IF(B25="","",MOD(INT(B25/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>400311002</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" spans="2:8">
-      <c r="B26" s="2">
-        <v>5011003</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="G26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>400311003</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="2:8">
+        <v>300344002</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
       <c r="B27" s="2">
-        <v>5011004</v>
+        <v>4044003</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>300344003</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="F28" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="2">
+        <v>5011001</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="2">
+        <f>IF(B29="","",INT(B29/1000000))</f>
         <v>5</v>
       </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>400311004</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="2:8">
-      <c r="B28" s="2">
-        <v>5011005</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>400311005</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" spans="2:8">
-      <c r="B29" s="2">
-        <v>5011006</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="2">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
       <c r="E29" s="2">
         <v>0</v>
       </c>
       <c r="F29" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>400311006</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" spans="2:8">
       <c r="B30" s="2">
+        <v>5011002</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" ref="D30:D35" si="4">IF(B30="","",INT(B30/1000000))</f>
+        <v>5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" ref="F30:F35" si="5">IF(B30="","",MOD(INT(B30/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>400311002</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" spans="2:8">
+      <c r="B31" s="2">
+        <v>5011003</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>400311003</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" spans="2:8">
+      <c r="B32" s="2">
+        <v>5011004</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>400311004</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="2:8">
+      <c r="B33" s="2">
+        <v>5011005</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>400311005</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="2:8">
+      <c r="B34" s="2">
+        <v>5011006</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>400311006</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="2:8">
+      <c r="B35" s="2">
         <v>5011007</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" si="3"/>
+      <c r="C35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="2">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
         <v>400311007</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="D31" s="2" t="str">
-        <f t="shared" ref="D31:D44" si="5">IF(B31="","",INT(B31/1000000))</f>
+    <row r="36" spans="2:8">
+      <c r="D36" s="2" t="str">
+        <f t="shared" ref="D36:D52" si="6">IF(B36="","",INT(B36/1000000))</f>
         <v/>
       </c>
-      <c r="F31" s="2" t="str">
-        <f t="shared" ref="F31:F44" si="6">IF(B31="","",MOD(INT(B31/1000),10))</f>
+      <c r="F36" s="2" t="str">
+        <f t="shared" ref="F36:F49" si="7">IF(B36="","",MOD(INT(B36/1000),10))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="B32" s="2">
+    <row r="37" spans="2:8">
+      <c r="B37" s="2">
         <v>6001001</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="2">
-        <f t="shared" si="5"/>
+      <c r="C37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="D33" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="F33" s="2" t="str">
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="D38" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2">
+      <c r="F38" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="2">
         <v>7024001</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="2">
-        <f t="shared" si="5"/>
+      <c r="C39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="2">
+        <v>7024002</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G34" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2">
-        <v>7024002</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="2">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E35" s="2">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="2">
+        <v>7024003</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G35" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2">
-        <v>7024003</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="2">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E36" s="2">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G36" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="D37" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="F37" s="2" t="str">
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="D42" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="2">
+      <c r="F42" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="2">
         <v>7034001</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="2">
-        <f t="shared" si="5"/>
+      <c r="C43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="2">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
-      <c r="F38" s="2">
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="2">
+        <v>7034002</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G38" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="2">
-        <v>7034002</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="2">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="2">
+        <v>7034003</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G39" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="2">
-        <v>7034003</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="2">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E40" s="2">
-        <v>0</v>
-      </c>
-      <c r="F40" s="2">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G40" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="D41" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="F41" s="2" t="str">
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="D46" s="2" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="2">
+      <c r="F46" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="2">
         <v>7044001</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="2">
-        <f t="shared" si="5"/>
+      <c r="C47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="2">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="E42" s="2">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="2">
+        <v>7044002</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G42" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="2">
-        <v>7044002</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="2">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="2">
+        <v>7044003</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G43" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="2">
-        <v>7044003</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="2">
-        <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="D50" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G44" s="2" t="b">
-        <v>0</v>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="2">
+        <v>8001001</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="2">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="2">
+        <v>8001002</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
+        <v>2</v>
+      </c>
+      <c r="J52" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G44" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G52" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:F3">
     <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:F3">
+  <conditionalFormatting sqref="G3">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B37">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  <conditionalFormatting sqref="B51">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  <conditionalFormatting sqref="B52">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
+  <conditionalFormatting sqref="B15:B16">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10:B11">
+  <conditionalFormatting sqref="B17:B20">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12:B15">
+  <conditionalFormatting sqref="B21:B27">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30:B35">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:B49">
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B22">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  <conditionalFormatting sqref="H17:H19">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25:B30">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="H21:H23">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B44">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H14">
+  <conditionalFormatting sqref="H25:H27">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16:H18">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20:H22">
+  <conditionalFormatting sqref="H30:H35">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H30">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B1:B3 B7 B9:B14 B36 B38 B42:B46 B50 B53:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9 B31 B33 B37:B41 B45:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15 H19">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="H20 H24">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -179,7 +179,34 @@
     <t>头像框-红</t>
   </si>
   <si>
-    <t>默认称号</t>
+    <t>从戎校尉</t>
+  </si>
+  <si>
+    <t>讨逆先锋</t>
+  </si>
+  <si>
+    <t>百战悍将</t>
+  </si>
+  <si>
+    <t>持节偏军</t>
+  </si>
+  <si>
+    <t>威武都督</t>
+  </si>
+  <si>
+    <t>镇国大将军</t>
+  </si>
+  <si>
+    <t>名震寰宇</t>
+  </si>
+  <si>
+    <t>兵圣传人</t>
+  </si>
+  <si>
+    <t>开国元勋</t>
+  </si>
+  <si>
+    <t>千古战神</t>
   </si>
   <si>
     <t>嬴政</t>
@@ -1400,7 +1427,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -2153,236 +2180,285 @@
     </row>
     <row r="36" spans="2:8">
       <c r="D36" s="2" t="str">
-        <f t="shared" ref="D36:D52" si="6">IF(B36="","",INT(B36/1000000))</f>
+        <f>IF(B36="","",INT(B36/1000000))</f>
         <v/>
       </c>
       <c r="F36" s="2" t="str">
-        <f t="shared" ref="F36:F49" si="7">IF(B36="","",MOD(INT(B36/1000),10))</f>
+        <f t="shared" ref="F36:F39" si="6">IF(B36="","",MOD(INT(B36/1000),10))</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="2">
-        <v>6001001</v>
+        <v>6011001</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D37" s="2">
+        <f>IF(B37="","",INT(B37/1000000))</f>
+        <v>6</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
         <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>500211001</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="2">
+        <v>6011002</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" ref="D38:D46" si="7">IF(B38="","",INT(B38/1000000))</f>
         <v>6</v>
       </c>
-      <c r="E37" s="2">
-        <v>0</v>
-      </c>
-      <c r="F37" s="2">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
-      <c r="D38" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="F38" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>500211002</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="2">
-        <v>7024001</v>
+        <v>6011003</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
         <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>500211003</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="2">
-        <v>7024002</v>
+        <v>6011004</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D40" s="2">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
       </c>
       <c r="F40" s="2">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>500211004</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="2">
-        <v>7024003</v>
+        <v>6011005</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
       </c>
       <c r="F41" s="2">
+        <f>IF(B41="","",MOD(INT(B41/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>500211005</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="2">
+        <v>6011006</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="2">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="G41" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8">
-      <c r="D42" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="F42" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>500211006</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="2">
-        <v>7034001</v>
+        <v>6011007</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
       </c>
       <c r="F43" s="2">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <f>IF(B43="","",MOD(INT(B43/1000),10))</f>
+        <v>1</v>
       </c>
       <c r="G43" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>500211007</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="2">
-        <v>7034002</v>
+        <v>6011008</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
       </c>
       <c r="F44" s="2">
-        <f t="shared" si="7"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>500211008</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="2">
-        <v>7034003</v>
+        <v>6011009</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
       </c>
       <c r="F45" s="2">
+        <f>IF(B45="","",MOD(INT(B45/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>500211009</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="2">
+        <v>6011010</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="2">
         <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="G45" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="D46" s="2" t="str">
-        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>500211010</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="D47" s="2" t="str">
+        <f t="shared" ref="D47:D61" si="8">IF(B47="","",INT(B47/1000000))</f>
         <v/>
       </c>
-      <c r="F46" s="2" t="str">
-        <f t="shared" si="7"/>
+      <c r="F47" s="2" t="str">
+        <f t="shared" ref="F47:F58" si="9">IF(B47="","",MOD(INT(B47/1000),10))</f>
         <v/>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="2">
-        <v>7044001</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="2">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="E47" s="2">
-        <v>0</v>
-      </c>
-      <c r="F47" s="2">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="G47" s="2" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="2">
-        <v>7044002</v>
+        <v>7024001</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
       </c>
       <c r="F48" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="G48" s="2" t="b">
@@ -2391,20 +2467,20 @@
     </row>
     <row r="49" spans="2:10">
       <c r="B49" s="2">
-        <v>7044003</v>
+        <v>7024002</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D49" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="E49" s="2">
         <v>0</v>
       </c>
       <c r="F49" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="G49" s="2" t="b">
@@ -2412,140 +2488,320 @@
       </c>
     </row>
     <row r="50" spans="2:10">
-      <c r="D50" s="2" t="str">
-        <f t="shared" si="6"/>
+      <c r="B50" s="2">
+        <v>7024003</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G50" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="D51" s="2" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="2">
-        <v>8001001</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="2">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="E51" s="2">
-        <v>0</v>
-      </c>
-      <c r="F51" s="2">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="2">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2">
-        <v>1</v>
+      <c r="F51" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v/>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="2">
+        <v>7034001</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="2">
+        <v>7034002</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="2">
+        <v>7034003</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G54" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="D55" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="2">
+        <v>7044001</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="2">
+        <v>7044002</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G57" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="B58" s="2">
+        <v>7044003</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="D59" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="B60" s="2">
+        <v>8001001</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
+      <c r="J60" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="B61" s="2">
         <v>8001002</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="2">
-        <f t="shared" si="6"/>
+      <c r="C61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="E52" s="2">
-        <v>0</v>
-      </c>
-      <c r="F52" s="2">
-        <v>1</v>
-      </c>
-      <c r="G52" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2">
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2">
         <v>2</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J61" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G52" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G61" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:F3">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
     <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:F3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  <conditionalFormatting sqref="B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B61">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:B16">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17:B20">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  <conditionalFormatting sqref="B21:B27">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  <conditionalFormatting sqref="B30:B35">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B41">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  <conditionalFormatting sqref="B37:B46">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B51">
+  <conditionalFormatting sqref="B56:B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17:H19">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H21:H23">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H27">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30:H35">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B3 B7 B9:B14 B36 B47 B51:B55 B59 B62:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20 H24">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37 H39 H41 H43 H45">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52">
+  <conditionalFormatting sqref="H38 H40 H42 H44 H46">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:B16">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:B20">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B27">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B35">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B47:B49">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H19">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H23">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H27">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H35">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B14 B36 B38 B42:B46 B50 B53:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H20 H24">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$64</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>铁矿</t>
+  </si>
+  <si>
+    <t>声望</t>
+  </si>
+  <si>
+    <t>功勋</t>
   </si>
   <si>
     <t>默认头像</t>
@@ -1427,7 +1433,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1727,128 +1733,112 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="2">
-        <v>4011001</v>
+        <v>1031001</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D15" s="2">
-        <f>IF(B15="","",INT(B15/1000000))</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="2">
+        <v>1031002</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="2">
+        <v>4011001</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="2">
+        <f>IF(B18="","",INT(B18/1000000))</f>
         <v>4</v>
       </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" ref="F15:F29" si="2">IF(B15="","",MOD(INT(B15/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:10">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="str">
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" ref="F18:F32" si="2">IF(B18="","",MOD(INT(B18/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:8">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:8">
-      <c r="B17" s="2">
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="2:8">
+      <c r="B20" s="2">
         <v>4024001</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="2">
-        <f>IF(B17="","",INT(B17/1000000))</f>
+      <c r="C20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2">
+        <f>IF(B20="","",INT(B20/1000000))</f>
         <v>4</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
         <v>300324001</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:8">
-      <c r="B18" s="2">
-        <v>4024002</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" ref="D17:D27" si="3">IF(B18="","",INT(B18/1000000))</f>
-        <v>4</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>300324002</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:8">
-      <c r="B19" s="2">
-        <v>4024003</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>300324003</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
-      <c r="F20" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v/>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" spans="2:8">
       <c r="B21" s="2">
-        <v>4034001</v>
+        <v>4024002</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D20:D30" si="3">IF(B21="","",INT(B21/1000000))</f>
         <v>4</v>
       </c>
       <c r="E21" s="2">
@@ -1862,12 +1852,12 @@
         <v>0</v>
       </c>
       <c r="H21" s="2">
-        <v>300334001</v>
+        <v>300324002</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" spans="2:8">
       <c r="B22" s="2">
-        <v>4034002</v>
+        <v>4024003</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>37</v>
@@ -1887,47 +1877,43 @@
         <v>0</v>
       </c>
       <c r="H22" s="2">
-        <v>300334002</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="2">
-        <v>4034003</v>
-      </c>
-      <c r="C23" s="2" t="s">
+        <v>300324003</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="2:8">
+      <c r="F23" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" spans="2:8">
+      <c r="B24" s="2">
+        <v>4034001</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D24" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>300334003</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="D24" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="F24" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>300334001</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="2:8">
       <c r="B25" s="2">
-        <v>4044001</v>
+        <v>4034002</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>39</v>
@@ -1947,12 +1933,12 @@
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <v>300344001</v>
+        <v>300334002</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="2">
-        <v>4044002</v>
+        <v>4034003</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>40</v>
@@ -1972,168 +1958,153 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>300344002</v>
+        <v>300334003</v>
       </c>
     </row>
     <row r="27" spans="2:8">
-      <c r="B27" s="2">
-        <v>4044003</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="2">
+        <v>4044001</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D28" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>300344001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="2">
+        <v>4044002</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>300344002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="2">
+        <v>4044003</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
         <v>300344003</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="F28" s="2" t="str">
+    <row r="31" spans="2:8">
+      <c r="F31" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="2">
+    <row r="32" spans="2:8">
+      <c r="B32" s="2">
         <v>5011001</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="2">
-        <f>IF(B29="","",INT(B29/1000000))</f>
+      <c r="C32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="2">
+        <f>IF(B32="","",INT(B32/1000000))</f>
         <v>5</v>
       </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G29" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="2:8">
-      <c r="B30" s="2">
-        <v>5011002</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" ref="D30:D35" si="4">IF(B30="","",INT(B30/1000000))</f>
-        <v>5</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <f t="shared" ref="F30:F35" si="5">IF(B30="","",MOD(INT(B30/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>400311002</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="2:8">
-      <c r="B31" s="2">
-        <v>5011003</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="2">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
-        <v>400311003</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="2:8">
-      <c r="B32" s="2">
-        <v>5011004</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="2">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>400311004</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" spans="2:8">
       <c r="B33" s="2">
-        <v>5011005</v>
+        <v>5011002</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D33:D40" si="4">IF(B33="","",INT(B33/1000000))</f>
         <v>5</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F33:F38" si="5">IF(B33="","",MOD(INT(B33/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>400311005</v>
+        <v>400311002</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" spans="2:8">
       <c r="B34" s="2">
-        <v>5011006</v>
+        <v>5011003</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" s="2">
         <f t="shared" si="4"/>
@@ -2150,15 +2121,15 @@
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>400311006</v>
+        <v>400311003</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" spans="2:8">
       <c r="B35" s="2">
-        <v>5011007</v>
+        <v>5011004</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2">
         <f t="shared" si="4"/>
@@ -2175,148 +2146,149 @@
         <v>0</v>
       </c>
       <c r="H35" s="2">
-        <v>400311007</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="D36" s="2" t="str">
-        <f>IF(B36="","",INT(B36/1000000))</f>
-        <v/>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" ref="F36:F39" si="6">IF(B36="","",MOD(INT(B36/1000),10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="2:8">
+        <v>400311004</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="2:8">
+      <c r="B36" s="2">
+        <v>5011005</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>400311005</v>
+      </c>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="2:8">
       <c r="B37" s="2">
-        <v>6011001</v>
+        <v>5011006</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D37" s="2">
-        <f>IF(B37="","",INT(B37/1000000))</f>
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>500211001</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8">
+        <v>400311006</v>
+      </c>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="2:8">
       <c r="B38" s="2">
-        <v>6011002</v>
+        <v>5011007</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D38" s="2">
-        <f t="shared" ref="D38:D46" si="7">IF(B38="","",INT(B38/1000000))</f>
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
       </c>
       <c r="F38" s="2">
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>500211002</v>
+        <v>400311007</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="2">
-        <v>6011003</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="2">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
-        <v>500211003</v>
+      <c r="D39" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f t="shared" ref="F39:F42" si="6">IF(B39="","",MOD(INT(B39/1000),10))</f>
+        <v/>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="2">
-        <v>6011004</v>
+        <v>6011001</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
       </c>
       <c r="F40" s="2">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G40" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>500211004</v>
+        <v>500211001</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="2">
-        <v>6011005</v>
+        <v>6011002</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="D41:D49" si="7">IF(B41="","",INT(B41/1000000))</f>
         <v>6</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
       </c>
       <c r="F41" s="2">
-        <f>IF(B41="","",MOD(INT(B41/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2">
-        <v>500211005</v>
+        <v>500211002</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="2">
-        <v>6011006</v>
+        <v>6011003</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D42" s="2">
         <f t="shared" si="7"/>
@@ -2326,21 +2298,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="2">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>500211006</v>
+        <v>500211003</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="2">
-        <v>6011007</v>
+        <v>6011004</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="2">
         <f t="shared" si="7"/>
@@ -2350,22 +2323,21 @@
         <v>0</v>
       </c>
       <c r="F43" s="2">
-        <f>IF(B43="","",MOD(INT(B43/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>500211007</v>
+        <v>500211004</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="2">
-        <v>6011008</v>
+        <v>6011005</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="2">
         <f t="shared" si="7"/>
@@ -2375,21 +2347,22 @@
         <v>0</v>
       </c>
       <c r="F44" s="2">
+        <f>IF(B44="","",MOD(INT(B44/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H44" s="2">
-        <v>500211008</v>
+        <v>500211005</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="2">
-        <v>6011009</v>
+        <v>6011006</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" s="2">
         <f t="shared" si="7"/>
@@ -2399,22 +2372,21 @@
         <v>0</v>
       </c>
       <c r="F45" s="2">
-        <f>IF(B45="","",MOD(INT(B45/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H45" s="2">
-        <v>500211009</v>
+        <v>500211006</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="2">
-        <v>6011010</v>
+        <v>6011007</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D46" s="2">
         <f t="shared" si="7"/>
@@ -2424,104 +2396,124 @@
         <v>0</v>
       </c>
       <c r="F46" s="2">
+        <f>IF(B46="","",MOD(INT(B46/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <v>500211010</v>
+        <v>500211007</v>
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="D47" s="2" t="str">
-        <f t="shared" ref="D47:D61" si="8">IF(B47="","",INT(B47/1000000))</f>
-        <v/>
-      </c>
-      <c r="F47" s="2" t="str">
-        <f t="shared" ref="F47:F58" si="9">IF(B47="","",MOD(INT(B47/1000),10))</f>
-        <v/>
+      <c r="B47" s="2">
+        <v>6011008</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2">
+        <v>500211008</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="2">
-        <v>7024001</v>
+        <v>6011009</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D48" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <f>IF(B48="","",MOD(INT(B48/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>500211009</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="2">
+        <v>6011010</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2">
+        <v>500211010</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="D50" s="2" t="str">
+        <f t="shared" ref="D50:D64" si="8">IF(B50="","",INT(B50/1000000))</f>
+        <v/>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f t="shared" ref="F50:F61" si="9">IF(B50="","",MOD(INT(B50/1000),10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="2">
+        <v>7024001</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
-      <c r="F48" s="2">
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G48" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="2">
-        <v>7024002</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" s="2">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="E49" s="2">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="G49" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="2">
-        <v>7024003</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="2">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="G50" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="D51" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="F51" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="2">
-        <v>7034001</v>
+        <v>7024002</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>62</v>
@@ -2543,7 +2535,7 @@
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="2">
-        <v>7034002</v>
+        <v>7024003</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>63</v>
@@ -2564,40 +2556,40 @@
       </c>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="2">
-        <v>7034003</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="2">
+        <v>7034001</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="2">
+      <c r="D55" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G54" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="D55" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="F55" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="2">
-        <v>7044001</v>
+        <v>7034002</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>65</v>
@@ -2619,7 +2611,7 @@
     </row>
     <row r="57" spans="2:10">
       <c r="B57" s="2">
-        <v>7044002</v>
+        <v>7034003</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>66</v>
@@ -2640,89 +2632,143 @@
       </c>
     </row>
     <row r="58" spans="2:10">
-      <c r="B58" s="2">
-        <v>7044003</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="D58" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="F58" s="2" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="B59" s="2">
+        <v>7044001</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D58" s="2">
+      <c r="D59" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G58" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="D59" s="2" t="str">
+      <c r="G59" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="B60" s="2">
+        <v>7044002</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="B61" s="2">
+        <v>7044003</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
+      <c r="D62" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:10">
-      <c r="B60" s="2">
+    <row r="63" spans="2:10">
+      <c r="B63" s="2">
         <v>8001001</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="C63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="2">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="E60" s="2">
-        <v>0</v>
-      </c>
-      <c r="F60" s="2">
-        <v>1</v>
-      </c>
-      <c r="G60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" s="2">
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
+      <c r="B64" s="2">
         <v>8001002</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="C64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="2">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="E61" s="2">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <v>1</v>
-      </c>
-      <c r="G61" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" s="2">
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2">
         <v>2</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J64" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G64" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
@@ -2746,61 +2792,61 @@
   <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B31">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
+  <conditionalFormatting sqref="B32">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B53">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
+  <conditionalFormatting sqref="B63">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
+  <conditionalFormatting sqref="B64">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15:B16">
+  <conditionalFormatting sqref="B18:B19">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17:B20">
+  <conditionalFormatting sqref="B20:B23">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B27">
+  <conditionalFormatting sqref="B24:B30">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B35">
+  <conditionalFormatting sqref="B33:B38">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37:B46">
+  <conditionalFormatting sqref="B40:B49">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B56:B58">
+  <conditionalFormatting sqref="B59:B61">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H19">
+  <conditionalFormatting sqref="H20:H22">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H23">
+  <conditionalFormatting sqref="H24:H26">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H27">
+  <conditionalFormatting sqref="H28:H30">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H35">
+  <conditionalFormatting sqref="H33:H38">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B14 B36 B47 B51:B55 B59 B62:B1048576">
+  <conditionalFormatting sqref="B1:B3 B7 B9:B17 B39 B50 B54:B58 B62 B65:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20 H24">
+  <conditionalFormatting sqref="H23 H27">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37 H39 H41 H43 H45">
+  <conditionalFormatting sqref="H40 H42 H44 H46 H48">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38 H40 H42 H44 H46">
+  <conditionalFormatting sqref="H41 H43 H45 H47 H49">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -116,6 +116,120 @@
     <t>改名卡</t>
   </si>
   <si>
+    <t>默认头像</t>
+  </si>
+  <si>
+    <t>头像-嬴政</t>
+  </si>
+  <si>
+    <t>头像-刘彻</t>
+  </si>
+  <si>
+    <t>头像-李世民</t>
+  </si>
+  <si>
+    <t>头像-赵飞燕</t>
+  </si>
+  <si>
+    <t>头像-蔡文姬</t>
+  </si>
+  <si>
+    <t>头像-杨玉环</t>
+  </si>
+  <si>
+    <t>头像-白起</t>
+  </si>
+  <si>
+    <t>头像-张骞</t>
+  </si>
+  <si>
+    <t>头像-房玄龄</t>
+  </si>
+  <si>
+    <t>默认头像框</t>
+  </si>
+  <si>
+    <t>头像框-白</t>
+  </si>
+  <si>
+    <t>头像框-绿</t>
+  </si>
+  <si>
+    <t>头像框-蓝</t>
+  </si>
+  <si>
+    <t>头像框-紫</t>
+  </si>
+  <si>
+    <t>头像框-橙</t>
+  </si>
+  <si>
+    <t>头像框-红</t>
+  </si>
+  <si>
+    <t>从戎校尉</t>
+  </si>
+  <si>
+    <t>讨逆先锋</t>
+  </si>
+  <si>
+    <t>百战悍将</t>
+  </si>
+  <si>
+    <t>持节偏军</t>
+  </si>
+  <si>
+    <t>威武都督</t>
+  </si>
+  <si>
+    <t>镇国大将军</t>
+  </si>
+  <si>
+    <t>名震寰宇</t>
+  </si>
+  <si>
+    <t>兵圣传人</t>
+  </si>
+  <si>
+    <t>开国元勋</t>
+  </si>
+  <si>
+    <t>千古战神</t>
+  </si>
+  <si>
+    <t>嬴政</t>
+  </si>
+  <si>
+    <t>刘彻</t>
+  </si>
+  <si>
+    <t>李世民</t>
+  </si>
+  <si>
+    <t>赵飞燕</t>
+  </si>
+  <si>
+    <t>蔡文姬</t>
+  </si>
+  <si>
+    <t>杨玉环</t>
+  </si>
+  <si>
+    <t>白起</t>
+  </si>
+  <si>
+    <t>张骞</t>
+  </si>
+  <si>
+    <t>房玄龄</t>
+  </si>
+  <si>
+    <t>人物经验</t>
+  </si>
+  <si>
+    <t>vip经验</t>
+  </si>
+  <si>
     <t>粮食</t>
   </si>
   <si>
@@ -126,120 +240,6 @@
   </si>
   <si>
     <t>铁矿</t>
-  </si>
-  <si>
-    <t>默认头像</t>
-  </si>
-  <si>
-    <t>头像-嬴政</t>
-  </si>
-  <si>
-    <t>头像-刘彻</t>
-  </si>
-  <si>
-    <t>头像-李世民</t>
-  </si>
-  <si>
-    <t>头像-赵飞燕</t>
-  </si>
-  <si>
-    <t>头像-蔡文姬</t>
-  </si>
-  <si>
-    <t>头像-杨玉环</t>
-  </si>
-  <si>
-    <t>头像-白起</t>
-  </si>
-  <si>
-    <t>头像-张骞</t>
-  </si>
-  <si>
-    <t>头像-房玄龄</t>
-  </si>
-  <si>
-    <t>默认头像框</t>
-  </si>
-  <si>
-    <t>头像框-白</t>
-  </si>
-  <si>
-    <t>头像框-绿</t>
-  </si>
-  <si>
-    <t>头像框-蓝</t>
-  </si>
-  <si>
-    <t>头像框-紫</t>
-  </si>
-  <si>
-    <t>头像框-橙</t>
-  </si>
-  <si>
-    <t>头像框-红</t>
-  </si>
-  <si>
-    <t>从戎校尉</t>
-  </si>
-  <si>
-    <t>讨逆先锋</t>
-  </si>
-  <si>
-    <t>百战悍将</t>
-  </si>
-  <si>
-    <t>持节偏军</t>
-  </si>
-  <si>
-    <t>威武都督</t>
-  </si>
-  <si>
-    <t>镇国大将军</t>
-  </si>
-  <si>
-    <t>名震寰宇</t>
-  </si>
-  <si>
-    <t>兵圣传人</t>
-  </si>
-  <si>
-    <t>开国元勋</t>
-  </si>
-  <si>
-    <t>千古战神</t>
-  </si>
-  <si>
-    <t>嬴政</t>
-  </si>
-  <si>
-    <t>刘彻</t>
-  </si>
-  <si>
-    <t>李世民</t>
-  </si>
-  <si>
-    <t>赵飞燕</t>
-  </si>
-  <si>
-    <t>蔡文姬</t>
-  </si>
-  <si>
-    <t>杨玉环</t>
-  </si>
-  <si>
-    <t>白起</t>
-  </si>
-  <si>
-    <t>张骞</t>
-  </si>
-  <si>
-    <t>房玄龄</t>
-  </si>
-  <si>
-    <t>人物经验</t>
-  </si>
-  <si>
-    <t>vip经验</t>
   </si>
 </sst>
 </file>
@@ -1541,14 +1541,14 @@
         <v>24</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" ref="D4:D13" si="0">IF(B4="","",INT(B4/1000000))</f>
+        <f>IF(B4="","",INT(B4/1000000))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F9" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <f>IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G4" s="2" t="b">
@@ -1563,14 +1563,14 @@
         <v>25</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="0"/>
+        <f>IF(B5="","",INT(B5/1000000))</f>
         <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" si="1"/>
+        <f>IF(B5="","",MOD(INT(B5/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G5" s="2" t="b">
@@ -1585,14 +1585,14 @@
         <v>26</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
+        <f>IF(B6="","",INT(B6/1000000))</f>
         <v>1</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="1"/>
+        <f>IF(B6="","",MOD(INT(B6/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G6" s="2" t="b">
@@ -1601,11 +1601,11 @@
     </row>
     <row r="7" spans="1:10">
       <c r="D7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(B7="","",INT(B7/1000000))</f>
         <v/>
       </c>
       <c r="F7" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(B7="","",MOD(INT(B7/1000),10))</f>
         <v/>
       </c>
     </row>
@@ -1617,848 +1617,852 @@
         <v>27</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="0"/>
+        <f>IF(B8="","",INT(B8/1000000))</f>
         <v>1</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="1"/>
+        <f>IF(B8="","",MOD(INT(B8/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="D9" s="2" t="str">
+    <row r="10" spans="1:10">
+      <c r="B10" s="2">
+        <v>4011001</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="2">
+        <f>IF(B10="","",INT(B10/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" ref="F10:F24" si="0">IF(B10="","",MOD(INT(B10/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:10">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="F9" s="2" t="str">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:10">
+      <c r="B12" s="2">
+        <v>4024001</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2">
+        <f>IF(B12="","",INT(B12/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>300324001</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:10">
+      <c r="B13" s="2">
+        <v>4024002</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" ref="D12:D22" si="1">IF(B13="","",INT(B13/1000000))</f>
+        <v>4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>300324002</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" spans="1:10">
+      <c r="B14" s="2">
+        <v>4024003</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>300324003</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="F15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:10">
+      <c r="B16" s="2">
+        <v>4034001</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>300334001</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="2:8">
+      <c r="B17" s="2">
+        <v>4034002</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>300334002</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="2">
+        <v>4034003</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>300334003</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="D19" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="2">
-        <v>1021001</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="F19" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="2">
-        <v>1021002</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="2">
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="2">
+        <v>4044001</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="2">
-        <v>1021003</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>300344001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="2">
+        <v>4044002</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="2">
-        <v>1021004</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>300344002</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="2">
+        <v>4044003</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2">
-        <v>4011001</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="2">
-        <f>IF(B15="","",INT(B15/1000000))</f>
         <v>4</v>
       </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <f t="shared" ref="F15:F29" si="2">IF(B15="","",MOD(INT(B15/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:10">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="str">
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>300344003</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="F23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="2">
+        <v>5011001</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="2">
+        <f>IF(B24="","",INT(B24/1000000))</f>
+        <v>5</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" spans="2:8">
+      <c r="B25" s="2">
+        <v>5011002</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" ref="D25:D32" si="2">IF(B25="","",INT(B25/1000000))</f>
+        <v>5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" ref="F25:F30" si="3">IF(B25="","",MOD(INT(B25/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>400311002</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" spans="2:8">
+      <c r="B26" s="2">
+        <v>5011003</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>400311003</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" spans="2:8">
+      <c r="B27" s="2">
+        <v>5011004</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>400311004</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="2:8">
+      <c r="B28" s="2">
+        <v>5011005</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>400311005</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" spans="2:8">
+      <c r="B29" s="2">
+        <v>5011006</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>400311006</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" spans="2:8">
+      <c r="B30" s="2">
+        <v>5011007</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>400311007</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="D31" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:8">
-      <c r="B17" s="2">
-        <v>4024001</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="2">
-        <f>IF(B17="","",INT(B17/1000000))</f>
-        <v>4</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>300324001</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:8">
-      <c r="B18" s="2">
-        <v>4024002</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="2">
-        <f t="shared" ref="D17:D27" si="3">IF(B18="","",INT(B18/1000000))</f>
-        <v>4</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>300324002</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:8">
-      <c r="B19" s="2">
-        <v>4024003</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>300324003</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
-      <c r="F20" s="2" t="str">
-        <f t="shared" si="2"/>
+      <c r="F31" s="2" t="str">
+        <f t="shared" ref="F31:F34" si="4">IF(B31="","",MOD(INT(B31/1000),10))</f>
         <v/>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="2:8">
-      <c r="B21" s="2">
-        <v>4034001</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>300334001</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="2:8">
-      <c r="B22" s="2">
-        <v>4034002</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>300334002</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="2">
-        <v>4034003</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>300334003</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="D24" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="F24" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="2">
-        <v>4044001</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>300344001</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="2">
-        <v>4044002</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <v>300344002</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="2">
-        <v>4044003</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="2">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>300344003</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="F28" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="2">
-        <v>5011001</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="2">
-        <f>IF(B29="","",INT(B29/1000000))</f>
-        <v>5</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G29" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="2:8">
-      <c r="B30" s="2">
-        <v>5011002</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="2">
-        <f t="shared" ref="D30:D35" si="4">IF(B30="","",INT(B30/1000000))</f>
-        <v>5</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <f t="shared" ref="F30:F35" si="5">IF(B30="","",MOD(INT(B30/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>400311002</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" spans="2:8">
-      <c r="B31" s="2">
-        <v>5011003</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="2">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="G31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
-        <v>400311003</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" spans="2:8">
+    <row r="32" spans="2:8">
       <c r="B32" s="2">
-        <v>5011004</v>
+        <v>6011001</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D32" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="2">
-        <v>400311004</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="2:8">
+        <v>500211001</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
       <c r="B33" s="2">
-        <v>5011005</v>
+        <v>6011002</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D33" s="2">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" ref="D33:D41" si="5">IF(B33="","",INT(B33/1000000))</f>
+        <v>6</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
       </c>
       <c r="F33" s="2">
-        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>400311005</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="2:8">
+        <v>500211002</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
       <c r="B34" s="2">
-        <v>5011006</v>
+        <v>6011003</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="D34" s="2">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2">
-        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="G34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>400311006</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="2:8">
+        <v>500211003</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
       <c r="B35" s="2">
-        <v>5011007</v>
+        <v>6011004</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D35" s="2">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
       </c>
       <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
+        <v>500211004</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="2">
+        <v>6011005</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2">
-        <v>400311007</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="D36" s="2" t="str">
-        <f>IF(B36="","",INT(B36/1000000))</f>
-        <v/>
-      </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" ref="F36:F39" si="6">IF(B36="","",MOD(INT(B36/1000),10))</f>
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <f>IF(B36="","",MOD(INT(B36/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
+        <v>500211005</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="2">
-        <v>6011001</v>
+        <v>6011006</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2">
-        <f>IF(B37="","",INT(B37/1000000))</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="E37" s="2">
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H37" s="2">
-        <v>500211001</v>
+        <v>500211006</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="2">
-        <v>6011002</v>
+        <v>6011007</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2">
-        <f t="shared" ref="D38:D46" si="7">IF(B38="","",INT(B38/1000000))</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
       </c>
       <c r="F38" s="2">
+        <f>IF(B38="","",MOD(INT(B38/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="2">
-        <v>500211002</v>
+        <v>500211007</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="2">
-        <v>6011003</v>
+        <v>6011008</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D39" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="G39" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <v>500211003</v>
+        <v>500211008</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="2">
-        <v>6011004</v>
+        <v>6011009</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D40" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
       </c>
       <c r="F40" s="2">
+        <f>IF(B40="","",MOD(INT(B40/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G40" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H40" s="2">
-        <v>500211004</v>
+        <v>500211009</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="2">
-        <v>6011005</v>
+        <v>6011010</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
       </c>
       <c r="F41" s="2">
-        <f>IF(B41="","",MOD(INT(B41/1000),10))</f>
         <v>1</v>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2">
-        <v>500211005</v>
+        <v>500211010</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="2">
-        <v>6011006</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="2">
-        <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E42" s="2">
-        <v>0</v>
-      </c>
-      <c r="F42" s="2">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
-        <v>500211006</v>
+      <c r="D42" s="2" t="str">
+        <f t="shared" ref="D42:D56" si="6">IF(B42="","",INT(B42/1000000))</f>
+        <v/>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f t="shared" ref="F42:F53" si="7">IF(B42="","",MOD(INT(B42/1000),10))</f>
+        <v/>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="2">
-        <v>6011007</v>
+        <v>7024001</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D43" s="2">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
         <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
-      <c r="F43" s="2">
-        <f>IF(B43="","",MOD(INT(B43/1000),10))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G43" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <v>500211007</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="2">
-        <v>6011008</v>
+        <v>7024002</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D44" s="2">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2">
         <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
-      <c r="F44" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G44" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="H44" s="2">
-        <v>500211008</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="2">
-        <v>6011009</v>
+        <v>7024003</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D45" s="2">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
         <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E45" s="2">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2">
-        <f>IF(B45="","",MOD(INT(B45/1000),10))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H45" s="2">
-        <v>500211009</v>
-      </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="2">
-        <v>6011010</v>
-      </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="2">
+        <v>7034001</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D47" s="2">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2">
         <f t="shared" si="7"/>
-        <v>6</v>
-      </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
-      <c r="F46" s="2">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="2">
-        <v>500211010</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="D47" s="2" t="str">
-        <f t="shared" ref="D47:D61" si="8">IF(B47="","",INT(B47/1000000))</f>
-        <v/>
-      </c>
-      <c r="F47" s="2" t="str">
-        <f t="shared" ref="F47:F58" si="9">IF(B47="","",MOD(INT(B47/1000),10))</f>
-        <v/>
+        <v>4</v>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="2">
-        <v>7024001</v>
+        <v>7034002</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D48" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
       </c>
       <c r="F48" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="G48" s="2" t="b">
@@ -2467,20 +2471,20 @@
     </row>
     <row r="49" spans="2:10">
       <c r="B49" s="2">
-        <v>7024002</v>
+        <v>7034003</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D49" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E49" s="2">
         <v>0</v>
       </c>
       <c r="F49" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="G49" s="2" t="b">
@@ -2488,53 +2492,53 @@
       </c>
     </row>
     <row r="50" spans="2:10">
-      <c r="B50" s="2">
-        <v>7024003</v>
-      </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="2">
+        <v>7044001</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="2">
-        <f t="shared" si="8"/>
+      <c r="D51" s="2">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
-      <c r="F50" s="2">
-        <f t="shared" si="9"/>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="G50" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="D51" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="F51" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="2">
-        <v>7034001</v>
+        <v>7044002</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D52" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E52" s="2">
         <v>0</v>
       </c>
       <c r="F52" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="G52" s="2" t="b">
@@ -2543,20 +2547,20 @@
     </row>
     <row r="53" spans="2:10">
       <c r="B53" s="2">
-        <v>7034002</v>
+        <v>7044003</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D53" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E53" s="2">
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="G53" s="2" t="b">
@@ -2564,119 +2568,117 @@
       </c>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="2">
-        <v>7034003</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="2">
+        <v>8001001</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="2">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="G54" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="D55" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="F55" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v/>
+      <c r="D55" s="2">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
+      <c r="J55" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:10">
       <c r="B56" s="2">
-        <v>7044001</v>
+        <v>8001002</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D56" s="2">
-        <f t="shared" si="8"/>
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="E56" s="2">
         <v>0</v>
       </c>
       <c r="F56" s="2">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="2">
-        <v>7044002</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="2">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="E57" s="2">
-        <v>0</v>
-      </c>
-      <c r="F57" s="2">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="G57" s="2" t="b">
-        <v>0</v>
+      <c r="I56" s="2">
+        <v>2</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:10">
       <c r="B58" s="2">
-        <v>7044003</v>
+        <v>10001001</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="2">
+        <f>IF(B58="","",INT(B58/1000000))</f>
+        <v>10</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="B59" s="2">
+        <v>10001002</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D58" s="2">
-        <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
-      <c r="F58" s="2">
-        <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="G58" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="D59" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v/>
+      <c r="D59" s="2">
+        <f>IF(B59="","",INT(B59/1000000))</f>
+        <v>10</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="2:10">
       <c r="B60" s="2">
-        <v>8001001</v>
+        <v>10001003</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D60" s="2">
-        <f t="shared" si="8"/>
-        <v>8</v>
+        <f>IF(B60="","",INT(B60/1000000))</f>
+        <v>10</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
@@ -2686,24 +2688,18 @@
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
-      </c>
-      <c r="I60" s="2">
-        <v>1</v>
-      </c>
-      <c r="J60" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:10">
       <c r="B61" s="2">
-        <v>8001002</v>
+        <v>10001004</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D61" s="2">
-        <f t="shared" si="8"/>
-        <v>8</v>
+        <f>IF(B61="","",INT(B61/1000000))</f>
+        <v>10</v>
       </c>
       <c r="E61" s="2">
         <v>0</v>
@@ -2714,15 +2710,9 @@
       <c r="G61" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="I61" s="2">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G61" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G56" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
@@ -2746,61 +2736,61 @@
   <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B23">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
+  <conditionalFormatting sqref="B24">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B45">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
+  <conditionalFormatting sqref="B55">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B61">
+  <conditionalFormatting sqref="B56">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15:B16">
+  <conditionalFormatting sqref="B10:B11">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B17:B20">
+  <conditionalFormatting sqref="B12:B15">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:B27">
+  <conditionalFormatting sqref="B16:B22">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:B35">
+  <conditionalFormatting sqref="B25:B30">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37:B46">
+  <conditionalFormatting sqref="B32:B41">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B56:B58">
+  <conditionalFormatting sqref="B51:B53">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17:H19">
+  <conditionalFormatting sqref="H12:H14">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H21:H23">
+  <conditionalFormatting sqref="H16:H18">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H27">
+  <conditionalFormatting sqref="H20:H22">
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H30:H35">
+  <conditionalFormatting sqref="H25:H30">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B14 B36 B47 B51:B55 B59 B62:B1048576">
+  <conditionalFormatting sqref="B1:B3 B7 B9 B31 B42 B46:B50 B54 B57:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H20 H24">
+  <conditionalFormatting sqref="H15 H19">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H37 H39 H41 H43 H45">
+  <conditionalFormatting sqref="H32 H34 H36 H38 H40">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H38 H40 H42 H44 H46">
+  <conditionalFormatting sqref="H33 H35 H37 H39 H41">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -1649,7 +1649,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="2">
-        <v>1031001</v>
+        <v>1021001</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>28</v>
@@ -1669,7 +1669,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="2">
-        <v>1031002</v>
+        <v>1021002</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>

--- a/data/config/luban/config/general/item.xlsx
+++ b/data/config/luban/config/general/item.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$G$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$H$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>#name</t>
   </si>
   <si>
+    <t>#description</t>
+  </si>
+  <si>
     <t>item_type</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>物品名称</t>
   </si>
   <si>
+    <t>物品描述</t>
+  </si>
+  <si>
     <t>物品类型</t>
   </si>
   <si>
@@ -107,21 +113,36 @@
     <t>黄金</t>
   </si>
   <si>
+    <t>顶级货币（充值/活动），用于加速、购买特权</t>
+  </si>
+  <si>
     <t>白银</t>
   </si>
   <si>
+    <t>高级货币，用于将领俸禄、稀有道具购买</t>
+  </si>
+  <si>
     <t>铜钱</t>
   </si>
   <si>
+    <t>基础货币，用于市场买卖、低级招募</t>
+  </si>
+  <si>
     <t>改名卡</t>
   </si>
   <si>
     <t>声望</t>
   </si>
   <si>
+    <t>通过完成任务和事件获得，解锁高级爵位与特殊NPC互动</t>
+  </si>
+  <si>
     <t>功勋</t>
   </si>
   <si>
+    <t>通过PVP战斗和国家任务获得，用于兑换专属装备与称号</t>
+  </si>
+  <si>
     <t>默认头像</t>
   </si>
   <si>
@@ -236,16 +257,43 @@
     <t>vip经验</t>
   </si>
   <si>
+    <t>农田</t>
+  </si>
+  <si>
+    <t>伐木场</t>
+  </si>
+  <si>
+    <t>采石场</t>
+  </si>
+  <si>
+    <t>矿场</t>
+  </si>
+  <si>
+    <t>民居</t>
+  </si>
+  <si>
     <t>粮食</t>
   </si>
   <si>
+    <t>维持士兵和人口的基本需求，影响民心</t>
+  </si>
+  <si>
     <t>木材</t>
   </si>
   <si>
+    <t>建造和升级建筑的主要材料</t>
+  </si>
+  <si>
     <t>石头</t>
   </si>
   <si>
+    <t>建造城墙和防御工事的必需品</t>
+  </si>
+  <si>
     <t>铁矿</t>
+  </si>
+  <si>
+    <t>制造兵器和器械的必需品</t>
   </si>
 </sst>
 </file>
@@ -1433,20 +1481,21 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
-    <col min="4" max="6" width="26" style="2" customWidth="1"/>
-    <col min="7" max="7" width="40.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="15" style="2" customWidth="1"/>
-    <col min="9" max="10" width="12.25" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="29.1166666666667" style="2" customWidth="1"/>
+    <col min="5" max="7" width="26" style="2" customWidth="1"/>
+    <col min="8" max="8" width="40.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15" style="2" customWidth="1"/>
+    <col min="10" max="11" width="12.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1477,19 +1526,19 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -1498,1356 +1547,1504 @@
         <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:10">
+        <v>12</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:11">
       <c r="B4" s="2">
         <v>1001001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2">
-        <f t="shared" ref="D4:D13" si="0">IF(B4="","",INT(B4/1000000))</f>
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <f t="shared" ref="E4:E13" si="0">IF(B4="","",INT(B4/1000000))</f>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" ref="F4:F9" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" ref="G4:G9" si="1">IF(B4="","",MOD(INT(B4/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" s="2">
         <v>1001002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
       <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="H5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6" s="2">
         <v>1001003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
       <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="D7" s="2" t="str">
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="E7" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="F7" s="2" t="str">
+      <c r="G7" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="B8" s="2">
         <v>1011001</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="2">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
       <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="D9" s="2" t="str">
+      <c r="H8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="E9" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="F9" s="2" t="str">
+      <c r="G9" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="B10" s="2">
         <v>1021001</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="B11" s="2">
         <v>1021002</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="B13" s="2">
         <v>4011001</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="2">
+        <v>37</v>
+      </c>
+      <c r="E13" s="2">
         <f>IF(B13="","",INT(B13/1000000))</f>
         <v>4</v>
       </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
       <c r="F13" s="2">
-        <f t="shared" ref="F13:F27" si="2">IF(B13="","",MOD(INT(B13/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" ref="G13:G27" si="2">IF(B13="","",MOD(INT(B13/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:11">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2" t="str">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:11">
       <c r="B15" s="2">
         <v>4024001</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="2">
+        <v>38</v>
+      </c>
+      <c r="E15" s="2">
         <f>IF(B15="","",INT(B15/1000000))</f>
         <v>4</v>
       </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
       <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
         <v>300324001</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
+    <row r="16" s="2" customFormat="1" spans="1:11">
       <c r="B16" s="2">
         <v>4024002</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="2">
-        <f t="shared" ref="D15:D25" si="3">IF(B16="","",INT(B16/1000000))</f>
+        <v>39</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" ref="E15:E25" si="3">IF(B16="","",INT(B16/1000000))</f>
         <v>4</v>
       </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
       <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
+      <c r="H16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
         <v>300324002</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" spans="2:8">
+    <row r="17" s="2" customFormat="1" spans="2:9">
       <c r="B17" s="2">
         <v>4024003</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="2">
+        <v>40</v>
+      </c>
+      <c r="E17" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
       <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
+      <c r="H17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
         <v>300324003</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" spans="2:8">
-      <c r="F18" s="2" t="str">
+    <row r="18" s="2" customFormat="1" spans="2:9">
+      <c r="G18" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" spans="2:8">
+    <row r="19" s="2" customFormat="1" spans="2:9">
       <c r="B19" s="2">
         <v>4034001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="2">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
       <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
+      <c r="H19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
         <v>300334001</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="2:8">
+    <row r="20" s="2" customFormat="1" spans="2:9">
       <c r="B20" s="2">
         <v>4034002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="2">
+        <v>42</v>
+      </c>
+      <c r="E20" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
       <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
+      <c r="H20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
         <v>300334002</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:9">
       <c r="B21" s="2">
         <v>4034003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="2">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
       <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
+      <c r="H21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
         <v>300334003</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="D22" s="2" t="str">
+    <row r="22" spans="2:9">
+      <c r="E22" s="2" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="F22" s="2" t="str">
+      <c r="G22" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:9">
       <c r="B23" s="2">
         <v>4044001</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="2">
+        <v>44</v>
+      </c>
+      <c r="E23" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
       <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
+      <c r="H23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
         <v>300344001</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:9">
       <c r="B24" s="2">
         <v>4044002</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="2">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
       <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2">
+      <c r="H24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
         <v>300344002</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:9">
       <c r="B25" s="2">
         <v>4044003</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="2">
+        <v>46</v>
+      </c>
+      <c r="E25" s="2">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
       <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="G25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
+      <c r="H25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
         <v>300344003</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="F26" s="2" t="str">
+    <row r="26" spans="2:9">
+      <c r="G26" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:9">
       <c r="B27" s="2">
         <v>5011001</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="2">
+        <v>47</v>
+      </c>
+      <c r="E27" s="2">
         <f>IF(B27="","",INT(B27/1000000))</f>
         <v>5</v>
       </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
       <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G27" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" spans="2:8">
+      <c r="H27" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" spans="2:9">
       <c r="B28" s="2">
         <v>5011002</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="2">
-        <f t="shared" ref="D28:D35" si="4">IF(B28="","",INT(B28/1000000))</f>
+        <v>48</v>
+      </c>
+      <c r="E28" s="2">
+        <f t="shared" ref="E28:E35" si="4">IF(B28="","",INT(B28/1000000))</f>
         <v>5</v>
       </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
       <c r="F28" s="2">
-        <f t="shared" ref="F28:F33" si="5">IF(B28="","",MOD(INT(B28/1000),10))</f>
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" ref="G28:G33" si="5">IF(B28="","",MOD(INT(B28/1000),10))</f>
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
         <v>400311002</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="2:8">
+    <row r="29" s="2" customFormat="1" spans="2:9">
       <c r="B29" s="2">
         <v>5011003</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="2">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
       <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
+      <c r="H29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
         <v>400311003</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" spans="2:8">
+    <row r="30" s="2" customFormat="1" spans="2:9">
       <c r="B30" s="2">
         <v>5011004</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="2">
+        <v>50</v>
+      </c>
+      <c r="E30" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
       <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
+      <c r="H30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
         <v>400311004</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" spans="2:8">
+    <row r="31" s="2" customFormat="1" spans="2:9">
       <c r="B31" s="2">
         <v>5011005</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="2">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
       <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
+      <c r="H31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
         <v>400311005</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="2:8">
+    <row r="32" s="2" customFormat="1" spans="2:9">
       <c r="B32" s="2">
         <v>5011006</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="2">
+        <v>52</v>
+      </c>
+      <c r="E32" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
       <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
+      <c r="H32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
         <v>400311006</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" spans="2:8">
+    <row r="33" s="2" customFormat="1" spans="2:9">
       <c r="B33" s="2">
         <v>5011007</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="2">
+        <v>53</v>
+      </c>
+      <c r="E33" s="2">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="E33" s="2">
-        <v>0</v>
-      </c>
       <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="G33" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="2">
+      <c r="H33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
         <v>400311007</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
-      <c r="D34" s="2" t="str">
+    <row r="34" spans="2:9">
+      <c r="E34" s="2" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="F34" s="2" t="str">
-        <f t="shared" ref="F34:F37" si="6">IF(B34="","",MOD(INT(B34/1000),10))</f>
+      <c r="G34" s="2" t="str">
+        <f t="shared" ref="G34:G37" si="6">IF(B34="","",MOD(INT(B34/1000),10))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:9">
       <c r="B35" s="2">
         <v>6011001</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="2">
+        <v>54</v>
+      </c>
+      <c r="E35" s="2">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="E35" s="2">
-        <v>0</v>
-      </c>
       <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="G35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2">
+      <c r="H35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
         <v>500211001</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:9">
       <c r="B36" s="2">
         <v>6011002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="2">
-        <f t="shared" ref="D36:D44" si="7">IF(B36="","",INT(B36/1000000))</f>
+        <v>55</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" ref="E36:E44" si="7">IF(B36="","",INT(B36/1000000))</f>
         <v>6</v>
       </c>
-      <c r="E36" s="2">
-        <v>0</v>
-      </c>
       <c r="F36" s="2">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
         <v>500211002</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:9">
       <c r="B37" s="2">
         <v>6011003</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="2">
+        <v>56</v>
+      </c>
+      <c r="E37" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E37" s="2">
-        <v>0</v>
-      </c>
       <c r="F37" s="2">
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="G37" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2">
+      <c r="H37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
         <v>500211003</v>
       </c>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:9">
       <c r="B38" s="2">
         <v>6011004</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="2">
+        <v>57</v>
+      </c>
+      <c r="E38" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E38" s="2">
-        <v>0</v>
-      </c>
       <c r="F38" s="2">
-        <v>1</v>
-      </c>
-      <c r="G38" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
         <v>500211004</v>
       </c>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:9">
       <c r="B39" s="2">
         <v>6011005</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="2">
+        <v>58</v>
+      </c>
+      <c r="E39" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
       <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2">
         <f>IF(B39="","",MOD(INT(B39/1000),10))</f>
         <v>1</v>
       </c>
-      <c r="G39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
+      <c r="H39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
         <v>500211005</v>
       </c>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:9">
       <c r="B40" s="2">
         <v>6011006</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="2">
+        <v>59</v>
+      </c>
+      <c r="E40" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E40" s="2">
-        <v>0</v>
-      </c>
       <c r="F40" s="2">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
         <v>500211006</v>
       </c>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:9">
       <c r="B41" s="2">
         <v>6011007</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D41" s="2">
+        <v>60</v>
+      </c>
+      <c r="E41" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E41" s="2">
-        <v>0</v>
-      </c>
       <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2">
         <f>IF(B41="","",MOD(INT(B41/1000),10))</f>
         <v>1</v>
       </c>
-      <c r="G41" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="2">
+      <c r="H41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
         <v>500211007</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:9">
       <c r="B42" s="2">
         <v>6011008</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="2">
+        <v>61</v>
+      </c>
+      <c r="E42" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E42" s="2">
-        <v>0</v>
-      </c>
       <c r="F42" s="2">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
         <v>500211008</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:9">
       <c r="B43" s="2">
         <v>6011009</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="2">
+        <v>62</v>
+      </c>
+      <c r="E43" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E43" s="2">
-        <v>0</v>
-      </c>
       <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
         <f>IF(B43="","",MOD(INT(B43/1000),10))</f>
         <v>1</v>
       </c>
-      <c r="G43" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
+      <c r="H43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
         <v>500211009</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:9">
       <c r="B44" s="2">
         <v>6011010</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="2">
+        <v>63</v>
+      </c>
+      <c r="E44" s="2">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="E44" s="2">
-        <v>0</v>
-      </c>
       <c r="F44" s="2">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+      <c r="H44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
         <v>500211010</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
-      <c r="D45" s="2" t="str">
-        <f t="shared" ref="D45:D59" si="8">IF(B45="","",INT(B45/1000000))</f>
+    <row r="45" spans="2:9">
+      <c r="E45" s="2" t="str">
+        <f t="shared" ref="E45:E59" si="8">IF(B45="","",INT(B45/1000000))</f>
         <v/>
       </c>
-      <c r="F45" s="2" t="str">
-        <f t="shared" ref="F45:F56" si="9">IF(B45="","",MOD(INT(B45/1000),10))</f>
+      <c r="G45" s="2" t="str">
+        <f t="shared" ref="G45:G56" si="9">IF(B45="","",MOD(INT(B45/1000),10))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:9">
       <c r="B46" s="2">
         <v>7024001</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="2">
+        <v>64</v>
+      </c>
+      <c r="E46" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E46" s="2">
-        <v>0</v>
-      </c>
       <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G46" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
+      <c r="H46" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
       <c r="B47" s="2">
         <v>7024002</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D47" s="2">
+        <v>65</v>
+      </c>
+      <c r="E47" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E47" s="2">
-        <v>0</v>
-      </c>
       <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G47" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="H47" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
       <c r="B48" s="2">
         <v>7024003</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="2">
+        <v>66</v>
+      </c>
+      <c r="E48" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E48" s="2">
-        <v>0</v>
-      </c>
       <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G48" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="D49" s="2" t="str">
+      <c r="H48" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="E49" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="F49" s="2" t="str">
+      <c r="G49" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:11">
       <c r="B50" s="2">
         <v>7034001</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D50" s="2">
+        <v>67</v>
+      </c>
+      <c r="E50" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E50" s="2">
-        <v>0</v>
-      </c>
       <c r="F50" s="2">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G50" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
+      <c r="H50" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
       <c r="B51" s="2">
         <v>7034002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="2">
+        <v>68</v>
+      </c>
+      <c r="E51" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E51" s="2">
-        <v>0</v>
-      </c>
       <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G51" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10">
+      <c r="H51" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" s="2">
         <v>7034003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D52" s="2">
+        <v>69</v>
+      </c>
+      <c r="E52" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E52" s="2">
-        <v>0</v>
-      </c>
       <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G52" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="D53" s="2" t="str">
+      <c r="H52" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="E53" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="F53" s="2" t="str">
+      <c r="G53" s="2" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:11">
       <c r="B54" s="2">
         <v>7044001</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D54" s="2">
+        <v>70</v>
+      </c>
+      <c r="E54" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
       <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G54" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
+      <c r="H54" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" s="2">
         <v>7044002</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55" s="2">
+        <v>71</v>
+      </c>
+      <c r="E55" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E55" s="2">
-        <v>0</v>
-      </c>
       <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G55" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
+      <c r="H55" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" s="2">
         <v>7044003</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D56" s="2">
+        <v>72</v>
+      </c>
+      <c r="E56" s="2">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="E56" s="2">
-        <v>0</v>
-      </c>
       <c r="F56" s="2">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="G56" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="D57" s="2" t="str">
+      <c r="H56" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="E57" s="2" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:11">
       <c r="B58" s="2">
         <v>8001001</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" s="2">
+        <v>73</v>
+      </c>
+      <c r="E58" s="2">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="E58" s="2">
-        <v>0</v>
-      </c>
       <c r="F58" s="2">
-        <v>1</v>
-      </c>
-      <c r="G58" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="b">
+        <v>0</v>
       </c>
       <c r="J58" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="2:10">
+      <c r="K58" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" s="2">
         <v>8001002</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" s="2">
+        <v>74</v>
+      </c>
+      <c r="E59" s="2">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="E59" s="2">
-        <v>0</v>
-      </c>
       <c r="F59" s="2">
-        <v>1</v>
-      </c>
-      <c r="G59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2">
         <v>2</v>
       </c>
-      <c r="J59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
+      <c r="K59" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="E60" s="2" t="str">
+        <f t="shared" ref="E60:E65" si="10">IF(B60="","",INT(B60/1000000))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
       <c r="B61" s="2">
+        <v>9011001</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="2">
+        <v>9021002</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="F62" s="2">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="2">
+        <v>9031003</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="2">
+        <v>9041004</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" s="2">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
+      <c r="B65" s="2">
+        <v>9051005</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8">
+      <c r="B67" s="2">
         <v>10001001</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D61" s="2">
-        <f>IF(B61="","",INT(B61/1000000))</f>
+      <c r="C67" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" s="2">
+        <f>IF(B67="","",INT(B67/1000000))</f>
         <v>10</v>
       </c>
-      <c r="E61" s="2">
-        <v>0</v>
-      </c>
-      <c r="F61" s="2">
-        <v>1</v>
-      </c>
-      <c r="G61" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10">
-      <c r="B62" s="2">
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8">
+      <c r="B68" s="2">
         <v>10001002</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="2">
-        <f>IF(B62="","",INT(B62/1000000))</f>
+      <c r="C68" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E68" s="2">
+        <f>IF(B68="","",INT(B68/1000000))</f>
         <v>10</v>
       </c>
-      <c r="E62" s="2">
-        <v>0</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10">
-      <c r="B63" s="2">
+      <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <v>1</v>
+      </c>
+      <c r="H68" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8">
+      <c r="B69" s="2">
         <v>10001003</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" s="2">
-        <f>IF(B63="","",INT(B63/1000000))</f>
+      <c r="C69" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E69" s="2">
+        <f>IF(B69="","",INT(B69/1000000))</f>
         <v>10</v>
       </c>
-      <c r="E63" s="2">
-        <v>0</v>
-      </c>
-      <c r="F63" s="2">
-        <v>1</v>
-      </c>
-      <c r="G63" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10">
-      <c r="B64" s="2">
+      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2">
+        <v>1</v>
+      </c>
+      <c r="H69" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8">
+      <c r="B70" s="2">
         <v>10001004</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D64" s="2">
-        <f>IF(B64="","",INT(B64/1000000))</f>
+      <c r="C70" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" s="2">
+        <f>IF(B70="","",INT(B70/1000000))</f>
         <v>10</v>
       </c>
-      <c r="E64" s="2">
-        <v>0</v>
-      </c>
-      <c r="F64" s="2">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="b">
+      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:G59" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:H59" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:F3">
+  <conditionalFormatting sqref="F3:G3">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
     <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="B4">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="duplicateValues" dxfId="0" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
+  <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
     <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+  <conditionalFormatting sqref="B48">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B58">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B59">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B14">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  <conditionalFormatting sqref="B15:B18">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  <conditionalFormatting sqref="B19:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B58">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="B28:B33">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59">
+  <conditionalFormatting sqref="B35:B44">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:B14">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:B18">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B19:B25">
+  <conditionalFormatting sqref="B54:B56">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:B33">
+  <conditionalFormatting sqref="B61:B65">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15:I17">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19:I21">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:I25">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I28:I33">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B44">
+  <conditionalFormatting sqref="B1:B3 B7 B9:B12 B34 B45 B49:B53 B57 B60 B66:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18 I22">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I35 I37 I39 I41 I43">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54:B56">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H17">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19:H21">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H25">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H28:H33">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B7 B9:B12 B34 B45 B49:B53 B57 B60:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18 H22">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35 H37 H39 H41 H43">
+  <conditionalFormatting sqref="I36 I38 I40 I42 I44">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H36 H38 H40 H42 H44">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
